--- a/database/homes.xlsx
+++ b/database/homes.xlsx
@@ -595,7 +595,7 @@
         <v>Kumbanad, Thiruvalla, Pathanamthitta, Kerala, 689542, India</v>
       </c>
       <c r="L5" t="str">
-        <v>pending</v>
+        <v>active</v>
       </c>
       <c r="M5" t="b">
         <v>0</v>
